--- a/Test Code/OneAsMany Test/New/d.xlsx
+++ b/Test Code/OneAsMany Test/New/d.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\RemasterShips\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\OneAsMany Test\New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A7BD43-9AB9-4063-911A-9774EB073025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1528407A-618E-4135-A098-00CC02C27322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39750" yWindow="1050" windowWidth="27435" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="1410" windowWidth="33630" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ship Data'!$A$1:$P$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ship Data'!$A$1:$P$328</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="1183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5148" uniqueCount="1252">
   <si>
     <t>Name</t>
   </si>
@@ -3585,6 +3585,213 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Pungari Thresher_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>Hyperyacht Aurorum</t>
+  </si>
+  <si>
+    <t>Destroyer for Hire</t>
+  </si>
+  <si>
+    <t>Palatine</t>
+  </si>
+  <si>
+    <t>Command Barge</t>
+  </si>
+  <si>
+    <t>Marines-2, Stealth, Unique</t>
+  </si>
+  <si>
+    <t>Command Ship-1, Detector, Rare</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Palatine_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Hyperyacht Aurorum_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Palatine_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Hyperyacht Aurorum_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>Defence Hanger</t>
+  </si>
+  <si>
+    <t>Munitions Platform</t>
+  </si>
+  <si>
+    <t>Small Space Station</t>
+  </si>
+  <si>
+    <t>Ephyra</t>
+  </si>
+  <si>
+    <t>Nematocyst</t>
+  </si>
+  <si>
+    <t>Orbital Picket</t>
+  </si>
+  <si>
+    <t>Orbital Outpost</t>
+  </si>
+  <si>
+    <t>Defence Halo</t>
+  </si>
+  <si>
+    <t>Orbital Spire</t>
+  </si>
+  <si>
+    <t>Large Space Station</t>
+  </si>
+  <si>
+    <t>Gatestation</t>
+  </si>
+  <si>
+    <t>Grav Hook</t>
+  </si>
+  <si>
+    <t>Mothership, Shield 4+</t>
+  </si>
+  <si>
+    <t>Shield 4+</t>
+  </si>
+  <si>
+    <t>Anchor</t>
+  </si>
+  <si>
+    <t>Shuriken</t>
+  </si>
+  <si>
+    <t>Shield-4+, Gateship-0</t>
+  </si>
+  <si>
+    <t>Grand Station</t>
+  </si>
+  <si>
+    <t>Medium Space Station</t>
+  </si>
+  <si>
+    <t>Astrobotanical Outpost</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Defence Hanger_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Defence Hanger_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Munitions Platform_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/UCM/Munitions Platform_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Ephyra_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Ephyra_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Nematocyst_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SCO/Nematocyst_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Orbital Picket_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Orbital Picket_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Orbital Outpost_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Orbital Outpost_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Defence Halo_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Defence Halo_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Orbital Spire_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/PHR/Orbital Spire_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Gatestation_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Gatestation_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Grav Hook_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Grav Hook_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Anchor_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Anchor_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Shuriken_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Shuriken_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/RES/Grand Station_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/RES/Grand Station_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/RES/Astrobotanical Outpost_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/RES/Astrobotanical Outpost_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>Mesolite</t>
+  </si>
+  <si>
+    <t>Supercruiser</t>
+  </si>
+  <si>
+    <t>Natrolite</t>
+  </si>
+  <si>
+    <t>Spinel</t>
+  </si>
+  <si>
+    <t>Painite</t>
+  </si>
+  <si>
+    <t>Euclase</t>
+  </si>
+  <si>
+    <t>Boracite</t>
+  </si>
+  <si>
+    <t>Pocket Battleship</t>
+  </si>
+  <si>
+    <t>Worldstrider</t>
+  </si>
+  <si>
+    <t>Electrosurge Torus</t>
+  </si>
+  <si>
+    <t>Stellargate</t>
   </si>
 </sst>
 </file>
@@ -3944,8 +4151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:R312"/>
+  <dimension ref="A1:R337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -4022,7 +4228,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1164</v>
       </c>
@@ -4078,7 +4284,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4134,7 +4340,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4190,7 +4396,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4246,7 +4452,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -4302,7 +4508,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -4358,7 +4564,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -4414,7 +4620,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4470,7 +4676,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -4526,7 +4732,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -4582,7 +4788,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -4638,7 +4844,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -4694,7 +4900,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -4750,7 +4956,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -4806,7 +5012,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -4862,7 +5068,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -4918,7 +5124,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -4974,7 +5180,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -5030,7 +5236,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -5086,7 +5292,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>120</v>
       </c>
@@ -5142,7 +5348,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
@@ -5198,7 +5404,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -5254,7 +5460,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -5310,7 +5516,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>135</v>
       </c>
@@ -5366,7 +5572,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -5422,7 +5628,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>142</v>
       </c>
@@ -5478,7 +5684,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -5534,7 +5740,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -5590,7 +5796,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5646,7 +5852,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>156</v>
       </c>
@@ -5702,7 +5908,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>160</v>
       </c>
@@ -5758,7 +5964,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -5814,7 +6020,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>167</v>
       </c>
@@ -5870,7 +6076,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>170</v>
       </c>
@@ -5926,7 +6132,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>174</v>
       </c>
@@ -5982,7 +6188,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>177</v>
       </c>
@@ -6038,7 +6244,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>180</v>
       </c>
@@ -6094,7 +6300,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -6150,7 +6356,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -6206,7 +6412,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>192</v>
       </c>
@@ -6262,7 +6468,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>195</v>
       </c>
@@ -6318,7 +6524,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -6374,7 +6580,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>201</v>
       </c>
@@ -6430,7 +6636,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>205</v>
       </c>
@@ -6486,7 +6692,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>208</v>
       </c>
@@ -6542,7 +6748,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -6598,7 +6804,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>215</v>
       </c>
@@ -6654,7 +6860,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>218</v>
       </c>
@@ -6710,7 +6916,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>221</v>
       </c>
@@ -6766,7 +6972,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>227</v>
       </c>
@@ -6822,7 +7028,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>230</v>
       </c>
@@ -6878,7 +7084,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>233</v>
       </c>
@@ -6934,7 +7140,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>238</v>
       </c>
@@ -6990,7 +7196,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>242</v>
       </c>
@@ -7046,7 +7252,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>245</v>
       </c>
@@ -7102,7 +7308,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>247</v>
       </c>
@@ -7158,7 +7364,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>250</v>
       </c>
@@ -7214,7 +7420,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>253</v>
       </c>
@@ -7270,7 +7476,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>256</v>
       </c>
@@ -7326,7 +7532,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>260</v>
       </c>
@@ -7382,7 +7588,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>264</v>
       </c>
@@ -7438,7 +7644,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>269</v>
       </c>
@@ -7494,7 +7700,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>274</v>
       </c>
@@ -7550,7 +7756,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>279</v>
       </c>
@@ -7606,7 +7812,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>284</v>
       </c>
@@ -7662,7 +7868,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>289</v>
       </c>
@@ -7718,7 +7924,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>295</v>
       </c>
@@ -7774,7 +7980,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1132</v>
       </c>
@@ -7830,7 +8036,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1133</v>
       </c>
@@ -7886,7 +8092,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1134</v>
       </c>
@@ -7942,7 +8148,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1135</v>
       </c>
@@ -7998,7 +8204,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>315</v>
       </c>
@@ -8054,7 +8260,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>319</v>
       </c>
@@ -8110,7 +8316,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>323</v>
       </c>
@@ -8166,7 +8372,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>327</v>
       </c>
@@ -8222,7 +8428,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>330</v>
       </c>
@@ -8278,7 +8484,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>333</v>
       </c>
@@ -8334,7 +8540,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>338</v>
       </c>
@@ -8390,7 +8596,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>342</v>
       </c>
@@ -8446,7 +8652,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>345</v>
       </c>
@@ -8502,7 +8708,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>350</v>
       </c>
@@ -8558,7 +8764,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>354</v>
       </c>
@@ -8614,7 +8820,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>359</v>
       </c>
@@ -8670,7 +8876,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>364</v>
       </c>
@@ -8726,7 +8932,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>368</v>
       </c>
@@ -8782,7 +8988,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>371</v>
       </c>
@@ -8838,7 +9044,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>374</v>
       </c>
@@ -8894,7 +9100,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>377</v>
       </c>
@@ -8950,7 +9156,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>381</v>
       </c>
@@ -9006,7 +9212,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>384</v>
       </c>
@@ -9062,7 +9268,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>387</v>
       </c>
@@ -9118,7 +9324,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>390</v>
       </c>
@@ -9174,7 +9380,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>393</v>
       </c>
@@ -9230,7 +9436,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>396</v>
       </c>
@@ -9286,7 +9492,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>399</v>
       </c>
@@ -9342,7 +9548,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>402</v>
       </c>
@@ -9398,7 +9604,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>406</v>
       </c>
@@ -9454,7 +9660,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>409</v>
       </c>
@@ -9510,7 +9716,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>412</v>
       </c>
@@ -9566,7 +9772,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>415</v>
       </c>
@@ -9622,7 +9828,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>418</v>
       </c>
@@ -9678,7 +9884,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>422</v>
       </c>
@@ -9734,7 +9940,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>426</v>
       </c>
@@ -9790,7 +9996,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>429</v>
       </c>
@@ -9846,7 +10052,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>432</v>
       </c>
@@ -9902,7 +10108,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>435</v>
       </c>
@@ -9958,7 +10164,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>438</v>
       </c>
@@ -10014,7 +10220,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>441</v>
       </c>
@@ -10070,7 +10276,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>444</v>
       </c>
@@ -10126,7 +10332,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>447</v>
       </c>
@@ -10182,7 +10388,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>450</v>
       </c>
@@ -10238,7 +10444,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>453</v>
       </c>
@@ -10294,7 +10500,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>456</v>
       </c>
@@ -10350,7 +10556,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>459</v>
       </c>
@@ -10406,7 +10612,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>463</v>
       </c>
@@ -10462,7 +10668,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>467</v>
       </c>
@@ -10518,7 +10724,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>470</v>
       </c>
@@ -10574,7 +10780,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>473</v>
       </c>
@@ -10630,7 +10836,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>476</v>
       </c>
@@ -10686,7 +10892,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>479</v>
       </c>
@@ -10742,7 +10948,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1145</v>
       </c>
@@ -10798,7 +11004,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1146</v>
       </c>
@@ -10854,7 +11060,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1147</v>
       </c>
@@ -10910,7 +11116,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1148</v>
       </c>
@@ -10966,7 +11172,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>496</v>
       </c>
@@ -11022,7 +11228,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>499</v>
       </c>
@@ -11078,7 +11284,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>339</v>
       </c>
@@ -11134,7 +11340,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>97</v>
       </c>
@@ -11190,7 +11396,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>510</v>
       </c>
@@ -11246,7 +11452,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>514</v>
       </c>
@@ -11302,7 +11508,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>519</v>
       </c>
@@ -11358,7 +11564,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>524</v>
       </c>
@@ -11414,7 +11620,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>528</v>
       </c>
@@ -11470,7 +11676,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>533</v>
       </c>
@@ -11526,7 +11732,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>536</v>
       </c>
@@ -11582,7 +11788,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>541</v>
       </c>
@@ -11638,7 +11844,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>150</v>
       </c>
@@ -11694,7 +11900,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>161</v>
       </c>
@@ -11750,7 +11956,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>189</v>
       </c>
@@ -11806,7 +12012,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>555</v>
       </c>
@@ -11862,7 +12068,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>559</v>
       </c>
@@ -11918,7 +12124,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>562</v>
       </c>
@@ -11974,7 +12180,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>565</v>
       </c>
@@ -12030,7 +12236,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>570</v>
       </c>
@@ -12086,7 +12292,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>573</v>
       </c>
@@ -12142,7 +12348,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>576</v>
       </c>
@@ -12198,7 +12404,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>580</v>
       </c>
@@ -12254,7 +12460,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>584</v>
       </c>
@@ -12310,7 +12516,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>587</v>
       </c>
@@ -12366,7 +12572,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>590</v>
       </c>
@@ -12422,7 +12628,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>594</v>
       </c>
@@ -12478,7 +12684,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>597</v>
       </c>
@@ -12534,7 +12740,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>601</v>
       </c>
@@ -12590,7 +12796,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>604</v>
       </c>
@@ -12646,7 +12852,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>607</v>
       </c>
@@ -12702,7 +12908,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>610</v>
       </c>
@@ -12758,7 +12964,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>613</v>
       </c>
@@ -12814,7 +13020,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>617</v>
       </c>
@@ -12870,7 +13076,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>622</v>
       </c>
@@ -12926,7 +13132,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1149</v>
       </c>
@@ -12982,7 +13188,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1150</v>
       </c>
@@ -13038,7 +13244,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1151</v>
       </c>
@@ -13094,7 +13300,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1152</v>
       </c>
@@ -13150,7 +13356,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>640</v>
       </c>
@@ -13206,7 +13412,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>644</v>
       </c>
@@ -13262,7 +13468,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>649</v>
       </c>
@@ -13318,7 +13524,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>654</v>
       </c>
@@ -13374,7 +13580,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>657</v>
       </c>
@@ -13430,7 +13636,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>660</v>
       </c>
@@ -13486,7 +13692,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>663</v>
       </c>
@@ -13542,7 +13748,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>666</v>
       </c>
@@ -13598,7 +13804,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>669</v>
       </c>
@@ -13654,7 +13860,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>673</v>
       </c>
@@ -13710,7 +13916,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>677</v>
       </c>
@@ -13766,7 +13972,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>680</v>
       </c>
@@ -13822,7 +14028,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>683</v>
       </c>
@@ -13878,7 +14084,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>688</v>
       </c>
@@ -13934,7 +14140,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>691</v>
       </c>
@@ -13990,7 +14196,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>694</v>
       </c>
@@ -14046,7 +14252,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>697</v>
       </c>
@@ -14102,7 +14308,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>700</v>
       </c>
@@ -14158,7 +14364,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>703</v>
       </c>
@@ -14214,7 +14420,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>706</v>
       </c>
@@ -14270,7 +14476,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>709</v>
       </c>
@@ -14326,7 +14532,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>712</v>
       </c>
@@ -14382,7 +14588,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>715</v>
       </c>
@@ -14438,7 +14644,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>719</v>
       </c>
@@ -14494,7 +14700,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>722</v>
       </c>
@@ -14550,7 +14756,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>725</v>
       </c>
@@ -14606,7 +14812,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>728</v>
       </c>
@@ -14662,7 +14868,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>732</v>
       </c>
@@ -14718,7 +14924,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>736</v>
       </c>
@@ -14774,7 +14980,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>739</v>
       </c>
@@ -14830,7 +15036,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>742</v>
       </c>
@@ -14886,7 +15092,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>745</v>
       </c>
@@ -14942,7 +15148,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>748</v>
       </c>
@@ -14998,7 +15204,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>751</v>
       </c>
@@ -15054,7 +15260,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>754</v>
       </c>
@@ -15110,7 +15316,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>757</v>
       </c>
@@ -15166,7 +15372,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>760</v>
       </c>
@@ -15222,7 +15428,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>764</v>
       </c>
@@ -15278,7 +15484,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>767</v>
       </c>
@@ -15334,7 +15540,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>770</v>
       </c>
@@ -15390,7 +15596,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>773</v>
       </c>
@@ -15446,7 +15652,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>776</v>
       </c>
@@ -15502,7 +15708,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>779</v>
       </c>
@@ -15558,7 +15764,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1153</v>
       </c>
@@ -15614,7 +15820,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1154</v>
       </c>
@@ -15670,7 +15876,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1155</v>
       </c>
@@ -15726,7 +15932,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1156</v>
       </c>
@@ -15782,7 +15988,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>795</v>
       </c>
@@ -15838,7 +16044,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>799</v>
       </c>
@@ -15894,7 +16100,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>804</v>
       </c>
@@ -15950,7 +16156,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>809</v>
       </c>
@@ -16006,7 +16212,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>813</v>
       </c>
@@ -16062,7 +16268,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>816</v>
       </c>
@@ -16118,7 +16324,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>820</v>
       </c>
@@ -16174,7 +16380,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>823</v>
       </c>
@@ -16230,7 +16436,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>827</v>
       </c>
@@ -16286,7 +16492,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>832</v>
       </c>
@@ -16342,7 +16548,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>835</v>
       </c>
@@ -16398,7 +16604,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>839</v>
       </c>
@@ -16454,7 +16660,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>843</v>
       </c>
@@ -16510,7 +16716,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>847</v>
       </c>
@@ -16566,7 +16772,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>850</v>
       </c>
@@ -16622,7 +16828,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>853</v>
       </c>
@@ -16678,7 +16884,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>858</v>
       </c>
@@ -16734,7 +16940,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>862</v>
       </c>
@@ -16790,7 +16996,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>866</v>
       </c>
@@ -16846,7 +17052,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>869</v>
       </c>
@@ -16902,7 +17108,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>872</v>
       </c>
@@ -16958,7 +17164,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>875</v>
       </c>
@@ -17014,7 +17220,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>878</v>
       </c>
@@ -17070,7 +17276,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>883</v>
       </c>
@@ -17126,7 +17332,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>887</v>
       </c>
@@ -17182,7 +17388,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>890</v>
       </c>
@@ -17238,7 +17444,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>893</v>
       </c>
@@ -17294,7 +17500,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>896</v>
       </c>
@@ -17350,7 +17556,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>900</v>
       </c>
@@ -17406,7 +17612,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>903</v>
       </c>
@@ -17462,7 +17668,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>906</v>
       </c>
@@ -17518,7 +17724,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>909</v>
       </c>
@@ -17574,7 +17780,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1140</v>
       </c>
@@ -17630,7 +17836,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1141</v>
       </c>
@@ -17686,7 +17892,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1144</v>
       </c>
@@ -17742,7 +17948,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1143</v>
       </c>
@@ -17798,7 +18004,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1142</v>
       </c>
@@ -17854,7 +18060,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>922</v>
       </c>
@@ -17910,7 +18116,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>925</v>
       </c>
@@ -17966,7 +18172,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>928</v>
       </c>
@@ -18022,7 +18228,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>931</v>
       </c>
@@ -18078,7 +18284,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>934</v>
       </c>
@@ -18134,7 +18340,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>937</v>
       </c>
@@ -18190,7 +18396,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>940</v>
       </c>
@@ -18246,7 +18452,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>943</v>
       </c>
@@ -18302,7 +18508,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>947</v>
       </c>
@@ -18358,7 +18564,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>950</v>
       </c>
@@ -18414,7 +18620,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>955</v>
       </c>
@@ -18470,7 +18676,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>959</v>
       </c>
@@ -18526,7 +18732,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>964</v>
       </c>
@@ -18582,7 +18788,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>968</v>
       </c>
@@ -18638,7 +18844,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>974</v>
       </c>
@@ -18694,7 +18900,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>977</v>
       </c>
@@ -18750,7 +18956,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>981</v>
       </c>
@@ -18806,7 +19012,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>986</v>
       </c>
@@ -18862,7 +19068,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>991</v>
       </c>
@@ -18918,7 +19124,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>994</v>
       </c>
@@ -18974,7 +19180,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>997</v>
       </c>
@@ -19030,7 +19236,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1000</v>
       </c>
@@ -19086,7 +19292,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1003</v>
       </c>
@@ -19142,7 +19348,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1007</v>
       </c>
@@ -19198,7 +19404,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1010</v>
       </c>
@@ -19254,7 +19460,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1014</v>
       </c>
@@ -19310,7 +19516,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1017</v>
       </c>
@@ -19366,7 +19572,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1020</v>
       </c>
@@ -19422,7 +19628,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1023</v>
       </c>
@@ -19478,7 +19684,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1027</v>
       </c>
@@ -19534,7 +19740,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1030</v>
       </c>
@@ -19590,7 +19796,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1033</v>
       </c>
@@ -19646,7 +19852,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1036</v>
       </c>
@@ -19702,7 +19908,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1039</v>
       </c>
@@ -19758,7 +19964,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1042</v>
       </c>
@@ -19814,7 +20020,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1045</v>
       </c>
@@ -19870,7 +20076,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1048</v>
       </c>
@@ -19926,7 +20132,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1051</v>
       </c>
@@ -19982,7 +20188,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1054</v>
       </c>
@@ -20038,7 +20244,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1057</v>
       </c>
@@ -20094,7 +20300,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1157</v>
       </c>
@@ -20150,7 +20356,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1063</v>
       </c>
@@ -20206,7 +20412,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1066</v>
       </c>
@@ -20262,7 +20468,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1069</v>
       </c>
@@ -20318,7 +20524,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1072</v>
       </c>
@@ -20374,7 +20580,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1075</v>
       </c>
@@ -20430,7 +20636,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1078</v>
       </c>
@@ -20486,7 +20692,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1081</v>
       </c>
@@ -20542,7 +20748,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1084</v>
       </c>
@@ -20598,7 +20804,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1087</v>
       </c>
@@ -20654,7 +20860,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1090</v>
       </c>
@@ -20710,7 +20916,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1094</v>
       </c>
@@ -20766,7 +20972,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1098</v>
       </c>
@@ -20822,7 +21028,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1101</v>
       </c>
@@ -20878,7 +21084,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1104</v>
       </c>
@@ -20934,7 +21140,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1107</v>
       </c>
@@ -20990,7 +21196,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1110</v>
       </c>
@@ -21046,7 +21252,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1114</v>
       </c>
@@ -21102,7 +21308,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1117</v>
       </c>
@@ -21158,7 +21364,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1120</v>
       </c>
@@ -21214,7 +21420,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1123</v>
       </c>
@@ -21270,7 +21476,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1126</v>
       </c>
@@ -21326,7 +21532,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1129</v>
       </c>
@@ -21369,7 +21575,7 @@
       <c r="N311" t="s">
         <v>946</v>
       </c>
-      <c r="O311" t="s">
+      <c r="O311" s="2" t="s">
         <v>1130</v>
       </c>
       <c r="P311" t="s">
@@ -21431,15 +21637,1393 @@
       <c r="P312" s="2" t="s">
         <v>1182</v>
       </c>
+      <c r="Q312" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R312" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B313">
+        <v>80</v>
+      </c>
+      <c r="C313" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D313">
+        <v>40</v>
+      </c>
+      <c r="E313">
+        <v>9</v>
+      </c>
+      <c r="F313">
+        <v>6</v>
+      </c>
+      <c r="G313">
+        <v>4</v>
+      </c>
+      <c r="H313">
+        <v>6</v>
+      </c>
+      <c r="I313">
+        <v>4</v>
+      </c>
+      <c r="J313">
+        <v>5</v>
+      </c>
+      <c r="K313">
+        <v>6</v>
+      </c>
+      <c r="L313">
+        <v>1</v>
+      </c>
+      <c r="M313" t="s">
+        <v>1187</v>
+      </c>
+      <c r="N313" t="s">
+        <v>241</v>
+      </c>
+      <c r="O313" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="P313" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="Q313" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R313" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B314">
+        <v>170</v>
+      </c>
+      <c r="C314" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D314">
+        <v>50</v>
+      </c>
+      <c r="E314">
+        <v>7</v>
+      </c>
+      <c r="F314">
+        <v>12</v>
+      </c>
+      <c r="G314">
+        <v>6</v>
+      </c>
+      <c r="H314">
+        <v>14</v>
+      </c>
+      <c r="I314">
+        <v>3</v>
+      </c>
+      <c r="J314">
+        <v>4</v>
+      </c>
+      <c r="K314">
+        <v>5</v>
+      </c>
+      <c r="L314">
+        <v>1</v>
+      </c>
+      <c r="M314" t="s">
+        <v>1188</v>
+      </c>
+      <c r="N314" t="s">
+        <v>241</v>
+      </c>
+      <c r="O314" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="P314" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="Q314" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R314" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B315">
+        <v>50</v>
+      </c>
+      <c r="C315" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D315">
+        <v>30</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>6</v>
+      </c>
+      <c r="G315">
+        <v>4</v>
+      </c>
+      <c r="H315">
+        <v>8</v>
+      </c>
+      <c r="I315">
+        <v>3</v>
+      </c>
+      <c r="J315">
+        <v>5</v>
+      </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
+      <c r="L315">
+        <v>1</v>
+      </c>
+      <c r="N315" t="s">
+        <v>946</v>
+      </c>
+      <c r="O315" t="s">
+        <v>1213</v>
+      </c>
+      <c r="P315" t="s">
+        <v>1214</v>
+      </c>
+      <c r="Q315" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R315" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B316">
+        <v>60</v>
+      </c>
+      <c r="C316" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D316">
+        <v>30</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>6</v>
+      </c>
+      <c r="G316">
+        <v>4</v>
+      </c>
+      <c r="H316">
+        <v>8</v>
+      </c>
+      <c r="I316">
+        <v>3</v>
+      </c>
+      <c r="J316">
+        <v>5</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>1</v>
+      </c>
+      <c r="N316" t="s">
+        <v>946</v>
+      </c>
+      <c r="O316" t="s">
+        <v>1215</v>
+      </c>
+      <c r="P316" t="s">
+        <v>1216</v>
+      </c>
+      <c r="Q316" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R316" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B317">
+        <v>65</v>
+      </c>
+      <c r="C317" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D317">
+        <v>30</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>6</v>
+      </c>
+      <c r="G317">
+        <v>4</v>
+      </c>
+      <c r="H317">
+        <v>8</v>
+      </c>
+      <c r="I317">
+        <v>3</v>
+      </c>
+      <c r="J317">
+        <v>4</v>
+      </c>
+      <c r="K317">
+        <v>0</v>
+      </c>
+      <c r="L317">
+        <v>1</v>
+      </c>
+      <c r="N317" t="s">
+        <v>626</v>
+      </c>
+      <c r="O317" t="s">
+        <v>1217</v>
+      </c>
+      <c r="P317" t="s">
+        <v>1218</v>
+      </c>
+      <c r="Q317" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R317" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B318">
+        <v>65</v>
+      </c>
+      <c r="C318" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D318">
+        <v>30</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>12</v>
+      </c>
+      <c r="G318">
+        <v>4</v>
+      </c>
+      <c r="H318">
+        <v>8</v>
+      </c>
+      <c r="I318">
+        <v>3</v>
+      </c>
+      <c r="J318">
+        <v>4</v>
+      </c>
+      <c r="K318">
+        <v>0</v>
+      </c>
+      <c r="L318">
+        <v>1</v>
+      </c>
+      <c r="N318" t="s">
+        <v>626</v>
+      </c>
+      <c r="O318" t="s">
+        <v>1219</v>
+      </c>
+      <c r="P318" t="s">
+        <v>1220</v>
+      </c>
+      <c r="Q318" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R318" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B319">
+        <v>75</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>6</v>
+      </c>
+      <c r="G319">
+        <v>4</v>
+      </c>
+      <c r="H319">
+        <v>9</v>
+      </c>
+      <c r="I319">
+        <v>3</v>
+      </c>
+      <c r="J319">
+        <v>4</v>
+      </c>
+      <c r="K319">
+        <v>0</v>
+      </c>
+      <c r="L319">
+        <v>1</v>
+      </c>
+      <c r="N319" t="s">
+        <v>300</v>
+      </c>
+      <c r="O319" t="s">
+        <v>1221</v>
+      </c>
+      <c r="P319" t="s">
+        <v>1222</v>
+      </c>
+      <c r="Q319" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R319" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B320">
+        <v>75</v>
+      </c>
+      <c r="C320" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D320">
+        <v>30</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>6</v>
+      </c>
+      <c r="G320">
+        <v>4</v>
+      </c>
+      <c r="H320">
+        <v>9</v>
+      </c>
+      <c r="I320">
+        <v>3</v>
+      </c>
+      <c r="J320">
+        <v>4</v>
+      </c>
+      <c r="K320">
+        <v>0</v>
+      </c>
+      <c r="L320">
+        <v>1</v>
+      </c>
+      <c r="N320" t="s">
+        <v>300</v>
+      </c>
+      <c r="O320" t="s">
+        <v>1223</v>
+      </c>
+      <c r="P320" t="s">
+        <v>1224</v>
+      </c>
+      <c r="Q320" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R320" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B321">
+        <v>145</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D321">
+        <v>50</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>8</v>
+      </c>
+      <c r="G321">
+        <v>6</v>
+      </c>
+      <c r="H321">
+        <v>26</v>
+      </c>
+      <c r="I321">
+        <v>3</v>
+      </c>
+      <c r="J321">
+        <v>4</v>
+      </c>
+      <c r="K321">
+        <v>0</v>
+      </c>
+      <c r="L321">
+        <v>1</v>
+      </c>
+      <c r="N321" t="s">
+        <v>300</v>
+      </c>
+      <c r="O321" t="s">
+        <v>1225</v>
+      </c>
+      <c r="P321" t="s">
+        <v>1226</v>
+      </c>
+      <c r="Q321" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R321" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B322">
+        <v>145</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D322">
+        <v>50</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>8</v>
+      </c>
+      <c r="G322">
+        <v>6</v>
+      </c>
+      <c r="H322">
+        <v>26</v>
+      </c>
+      <c r="I322">
+        <v>3</v>
+      </c>
+      <c r="J322">
+        <v>4</v>
+      </c>
+      <c r="K322">
+        <v>0</v>
+      </c>
+      <c r="L322">
+        <v>1</v>
+      </c>
+      <c r="N322" t="s">
+        <v>300</v>
+      </c>
+      <c r="O322" t="s">
+        <v>1227</v>
+      </c>
+      <c r="P322" t="s">
+        <v>1228</v>
+      </c>
+      <c r="Q322" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R322" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B323">
+        <v>75</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D323">
+        <v>30</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>4</v>
+      </c>
+      <c r="G323">
+        <v>6</v>
+      </c>
+      <c r="H323">
+        <v>10</v>
+      </c>
+      <c r="I323">
+        <v>4</v>
+      </c>
+      <c r="J323">
+        <v>4</v>
+      </c>
+      <c r="K323">
+        <v>0</v>
+      </c>
+      <c r="L323">
+        <v>1</v>
+      </c>
+      <c r="M323" t="s">
+        <v>1205</v>
+      </c>
+      <c r="N323" t="s">
+        <v>782</v>
+      </c>
+      <c r="O323" t="s">
+        <v>1229</v>
+      </c>
+      <c r="P323" t="s">
+        <v>1230</v>
+      </c>
+      <c r="Q323" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R323" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B324">
+        <v>75</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D324">
+        <v>30</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>4</v>
+      </c>
+      <c r="G324">
+        <v>6</v>
+      </c>
+      <c r="H324">
+        <v>10</v>
+      </c>
+      <c r="I324">
+        <v>4</v>
+      </c>
+      <c r="J324">
+        <v>4</v>
+      </c>
+      <c r="K324">
+        <v>0</v>
+      </c>
+      <c r="L324">
+        <v>1</v>
+      </c>
+      <c r="M324" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N324" t="s">
+        <v>782</v>
+      </c>
+      <c r="O324" t="s">
+        <v>1231</v>
+      </c>
+      <c r="P324" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Q324" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R324" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B325">
+        <v>120</v>
+      </c>
+      <c r="C325" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D325">
+        <v>50</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>12</v>
+      </c>
+      <c r="G325">
+        <v>6</v>
+      </c>
+      <c r="H325">
+        <v>24</v>
+      </c>
+      <c r="I325">
+        <v>4</v>
+      </c>
+      <c r="J325">
+        <v>4</v>
+      </c>
+      <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
+        <v>1</v>
+      </c>
+      <c r="M325" t="s">
+        <v>1209</v>
+      </c>
+      <c r="N325" t="s">
+        <v>782</v>
+      </c>
+      <c r="O325" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="P325" t="s">
+        <v>1234</v>
+      </c>
+      <c r="Q325" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R325" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B326">
+        <v>150</v>
+      </c>
+      <c r="C326" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D326">
+        <v>50</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>12</v>
+      </c>
+      <c r="G326">
+        <v>6</v>
+      </c>
+      <c r="H326">
+        <v>24</v>
+      </c>
+      <c r="I326">
+        <v>4</v>
+      </c>
+      <c r="J326">
+        <v>4</v>
+      </c>
+      <c r="K326">
+        <v>0</v>
+      </c>
+      <c r="L326">
+        <v>1</v>
+      </c>
+      <c r="M326" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N326" t="s">
+        <v>782</v>
+      </c>
+      <c r="O326" t="s">
+        <v>1235</v>
+      </c>
+      <c r="P326" t="s">
+        <v>1236</v>
+      </c>
+      <c r="Q326" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R326" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B327">
+        <v>85</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D327">
+        <v>40</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>6</v>
+      </c>
+      <c r="G327">
+        <v>6</v>
+      </c>
+      <c r="H327">
+        <v>14</v>
+      </c>
+      <c r="I327">
+        <v>3</v>
+      </c>
+      <c r="J327">
+        <v>5</v>
+      </c>
+      <c r="K327">
+        <v>0</v>
+      </c>
+      <c r="L327">
+        <v>1</v>
+      </c>
+      <c r="N327" t="s">
+        <v>482</v>
+      </c>
+      <c r="O327" t="s">
+        <v>1237</v>
+      </c>
+      <c r="P327" t="s">
+        <v>1238</v>
+      </c>
+      <c r="Q327" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R327" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B328">
+        <v>85</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D328">
+        <v>40</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>6</v>
+      </c>
+      <c r="G328">
+        <v>6</v>
+      </c>
+      <c r="H328">
+        <v>14</v>
+      </c>
+      <c r="I328">
+        <v>3</v>
+      </c>
+      <c r="J328">
+        <v>5</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>1</v>
+      </c>
+      <c r="N328" t="s">
+        <v>482</v>
+      </c>
+      <c r="O328" t="s">
+        <v>1239</v>
+      </c>
+      <c r="P328" t="s">
+        <v>1240</v>
+      </c>
+      <c r="Q328" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R328" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B329">
+        <v>180</v>
+      </c>
+      <c r="C329" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D329">
+        <v>50</v>
+      </c>
+      <c r="E329">
+        <v>10</v>
+      </c>
+      <c r="F329">
+        <v>12</v>
+      </c>
+      <c r="G329">
+        <v>6</v>
+      </c>
+      <c r="H329">
+        <v>12</v>
+      </c>
+      <c r="I329">
+        <v>5</v>
+      </c>
+      <c r="J329">
+        <v>4</v>
+      </c>
+      <c r="K329">
+        <v>6</v>
+      </c>
+      <c r="L329">
+        <v>1</v>
+      </c>
+      <c r="M329" t="s">
+        <v>783</v>
+      </c>
+      <c r="N329" t="s">
+        <v>782</v>
+      </c>
+      <c r="O329" t="str">
+        <f>_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/",A329,"_ModelImage.png")</f>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Mesolite_ModelImage.png</v>
+      </c>
+      <c r="P329" t="str">
+        <f>_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/",A329,"_CardFrontImage.png")</f>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Mesolite_CardFrontImage.png</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R329" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B330">
+        <v>184</v>
+      </c>
+      <c r="C330" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D330">
+        <v>50</v>
+      </c>
+      <c r="E330">
+        <v>10</v>
+      </c>
+      <c r="F330">
+        <v>12</v>
+      </c>
+      <c r="G330">
+        <v>6</v>
+      </c>
+      <c r="H330">
+        <v>12</v>
+      </c>
+      <c r="I330">
+        <v>5</v>
+      </c>
+      <c r="J330">
+        <v>4</v>
+      </c>
+      <c r="K330">
+        <v>6</v>
+      </c>
+      <c r="L330">
+        <v>1</v>
+      </c>
+      <c r="M330" t="s">
+        <v>783</v>
+      </c>
+      <c r="N330" t="s">
+        <v>782</v>
+      </c>
+      <c r="O330" t="str">
+        <f t="shared" ref="O330:O337" si="0">_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/",A330,"_ModelImage.png")</f>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Natrolite_ModelImage.png</v>
+      </c>
+      <c r="P330" t="str">
+        <f>_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/",A330,"_CardFrontImage.png")</f>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Natrolite_CardFrontImage.png</v>
+      </c>
+      <c r="Q330" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R330" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B331">
+        <v>225</v>
+      </c>
+      <c r="C331" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D331">
+        <v>50</v>
+      </c>
+      <c r="E331">
+        <v>8</v>
+      </c>
+      <c r="F331">
+        <v>12</v>
+      </c>
+      <c r="G331">
+        <v>6</v>
+      </c>
+      <c r="H331">
+        <v>14</v>
+      </c>
+      <c r="I331">
+        <v>5</v>
+      </c>
+      <c r="J331">
+        <v>4</v>
+      </c>
+      <c r="K331">
+        <v>5</v>
+      </c>
+      <c r="L331">
+        <v>1</v>
+      </c>
+      <c r="M331" t="s">
+        <v>783</v>
+      </c>
+      <c r="N331" t="s">
+        <v>782</v>
+      </c>
+      <c r="O331" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Spinel_ModelImage.png</v>
+      </c>
+      <c r="P331" t="str">
+        <f t="shared" ref="P331:P337" si="1">_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/",A331,"_CardFrontImage.png")</f>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Spinel_CardFrontImage.png</v>
+      </c>
+      <c r="Q331" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R331" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B332">
+        <v>190</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D332">
+        <v>50</v>
+      </c>
+      <c r="E332">
+        <v>8</v>
+      </c>
+      <c r="F332">
+        <v>12</v>
+      </c>
+      <c r="G332">
+        <v>6</v>
+      </c>
+      <c r="H332">
+        <v>14</v>
+      </c>
+      <c r="I332">
+        <v>5</v>
+      </c>
+      <c r="J332">
+        <v>4</v>
+      </c>
+      <c r="K332">
+        <v>5</v>
+      </c>
+      <c r="L332">
+        <v>1</v>
+      </c>
+      <c r="M332" t="s">
+        <v>783</v>
+      </c>
+      <c r="N332" t="s">
+        <v>782</v>
+      </c>
+      <c r="O332" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Painite_ModelImage.png</v>
+      </c>
+      <c r="P332" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Painite_CardFrontImage.png</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R332" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B333">
+        <v>220</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D333">
+        <v>50</v>
+      </c>
+      <c r="E333">
+        <v>8</v>
+      </c>
+      <c r="F333">
+        <v>12</v>
+      </c>
+      <c r="G333">
+        <v>6</v>
+      </c>
+      <c r="H333">
+        <v>14</v>
+      </c>
+      <c r="I333">
+        <v>5</v>
+      </c>
+      <c r="J333">
+        <v>4</v>
+      </c>
+      <c r="K333">
+        <v>5</v>
+      </c>
+      <c r="L333">
+        <v>1</v>
+      </c>
+      <c r="M333" t="s">
+        <v>783</v>
+      </c>
+      <c r="N333" t="s">
+        <v>782</v>
+      </c>
+      <c r="O333" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Euclase_ModelImage.png</v>
+      </c>
+      <c r="P333" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Euclase_CardFrontImage.png</v>
+      </c>
+      <c r="Q333" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R333" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B334">
+        <v>200</v>
+      </c>
+      <c r="C334" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D334">
+        <v>50</v>
+      </c>
+      <c r="E334">
+        <v>8</v>
+      </c>
+      <c r="F334">
+        <v>12</v>
+      </c>
+      <c r="G334">
+        <v>6</v>
+      </c>
+      <c r="H334">
+        <v>14</v>
+      </c>
+      <c r="I334">
+        <v>5</v>
+      </c>
+      <c r="J334">
+        <v>4</v>
+      </c>
+      <c r="K334">
+        <v>5</v>
+      </c>
+      <c r="L334">
+        <v>1</v>
+      </c>
+      <c r="M334" t="s">
+        <v>783</v>
+      </c>
+      <c r="N334" t="s">
+        <v>782</v>
+      </c>
+      <c r="O334" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Boracite_ModelImage.png</v>
+      </c>
+      <c r="P334" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Boracite_CardFrontImage.png</v>
+      </c>
+      <c r="Q334" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R334" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D335">
+        <v>30</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>0</v>
+      </c>
+      <c r="G335">
+        <v>0</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335">
+        <v>0</v>
+      </c>
+      <c r="L335">
+        <v>1</v>
+      </c>
+      <c r="N335" t="s">
+        <v>782</v>
+      </c>
+      <c r="O335" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Worldstrider_ModelImage.png</v>
+      </c>
+      <c r="P335" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Worldstrider_CardFrontImage.png</v>
+      </c>
+      <c r="Q335" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R335" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D336">
+        <v>30</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>0</v>
+      </c>
+      <c r="G336">
+        <v>0</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>1</v>
+      </c>
+      <c r="N336" t="s">
+        <v>782</v>
+      </c>
+      <c r="O336" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Electrosurge Torus_ModelImage.png</v>
+      </c>
+      <c r="P336" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Electrosurge Torus_CardFrontImage.png</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R336" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D337">
+        <v>30</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>0</v>
+      </c>
+      <c r="G337">
+        <v>0</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>0</v>
+      </c>
+      <c r="L337">
+        <v>1</v>
+      </c>
+      <c r="N337" t="s">
+        <v>782</v>
+      </c>
+      <c r="O337" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Stellargate_ModelImage.png</v>
+      </c>
+      <c r="P337" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/SHA/Stellargate_CardFrontImage.png</v>
+      </c>
+      <c r="Q337" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R337" t="s">
+        <v>1168</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P312" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Hive Ship"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="O69" r:id="rId1" xr:uid="{199D85C6-8205-44AF-8889-1D194BB490BD}"/>
     <hyperlink ref="O70" r:id="rId2" xr:uid="{4C94DFDA-489B-476E-8AC6-E7F89E79353B}"/>
@@ -21470,6 +23054,12 @@
     <hyperlink ref="O58" r:id="rId27" xr:uid="{48D462A0-3134-48DE-AD12-1BB27C9D5DEB}"/>
     <hyperlink ref="O312" r:id="rId28" xr:uid="{DEF7037B-F289-4CE9-9E55-AD3BBE4D1DE8}"/>
     <hyperlink ref="P312" r:id="rId29" xr:uid="{AB01918B-B663-4449-BAA3-04E293229795}"/>
+    <hyperlink ref="O314" r:id="rId30" xr:uid="{2B322187-3165-47AA-A2B1-21E5B99C0C68}"/>
+    <hyperlink ref="O313" r:id="rId31" xr:uid="{1BA2B9C4-9FE6-473A-A16F-CFEFC2EC4C48}"/>
+    <hyperlink ref="P314" r:id="rId32" xr:uid="{C97B7914-82EE-402D-9D83-9F20DD679976}"/>
+    <hyperlink ref="P313" r:id="rId33" xr:uid="{2E843717-98E6-48B0-8415-7A7747E50455}"/>
+    <hyperlink ref="O311" r:id="rId34" xr:uid="{C3048C77-C426-4CAD-9EBB-AD0D20C3AE7B}"/>
+    <hyperlink ref="O325" r:id="rId35" xr:uid="{DE2F7D83-9AEF-45C0-BC31-FEBEFD8A07DE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
